--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_221_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_221_R23.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2774</v>
+        <v>3.4917</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5168</v>
+        <v>1.879</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2394</v>
+        <v>1.6127</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8245</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.664</v>
+        <v>0.2365</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1605</v>
+        <v>0.9635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3264</v>
+        <v>1.9226</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4097</v>
+        <v>1.2169</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7361</v>
+        <v>0.7057</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1509</v>
+        <v>-0.7226</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2543</v>
+        <v>-0.9804</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8966</v>
+        <v>0.2578</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8556</v>
+        <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1741</v>
+        <v>0.2763</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1181</v>
+        <v>0.6728</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.3965</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0722</v>
+        <v>-0.2525</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9731</v>
+        <v>2.3895</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3941</v>
+        <v>2.3936</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5791</v>
+        <v>-0.0041</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2</v>
+        <v>-0.8245</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2365</v>
+        <v>-0.664</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9635</v>
+        <v>-0.1605</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9226</v>
+        <v>0.3264</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2169</v>
+        <v>-0.4097</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7057</v>
+        <v>0.7361</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7226</v>
+        <v>-1.1509</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9804</v>
+        <v>-0.2543</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2578</v>
+        <v>-0.8966</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0154</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7578</v>
+        <v>0.2862</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1879</v>
+        <v>0.995</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4301</v>
+        <v>-0.7088</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2525</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1498</v>
+        <v>0.1072</v>
       </c>
       <c r="E4" t="n">
-        <v>1.12</v>
+        <v>1.3126</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9702</v>
+        <v>-1.2054</v>
       </c>
       <c r="G4" t="n">
         <v>1.7812</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.322</v>
+        <v>-0.3646</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2434</v>
+        <v>-0.0507</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0786</v>
+        <v>-0.3139</v>
       </c>
       <c r="V4" t="n">
         <v>-2.933</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3909</v>
+        <v>-0.6166</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9268999999999999</v>
+        <v>1.3987</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3178</v>
+        <v>-2.0153</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9545</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5239</v>
+        <v>-0.7497</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6247</v>
+        <v>-0.1529</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8992</v>
+        <v>-0.5968</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5361</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4049</v>
+        <v>-1.4572</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0315</v>
+        <v>-2.1845</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6266</v>
+        <v>0.7272</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1456</v>
+        <v>-0.6106</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8942</v>
+        <v>-0.383</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2514</v>
+        <v>-0.2276</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4793</v>
+        <v>1.6987</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1275</v>
+        <v>1.2372</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3519</v>
+        <v>0.4615</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6663</v>
+        <v>-2.3094</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7667</v>
+        <v>-1.6203</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1005</v>
+        <v>-0.6891</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6237</v>
+        <v>-3.9432</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>3.4793</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9726</v>
+        <v>-0.9188</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3936</v>
+        <v>-0.2236</v>
       </c>
       <c r="U6" t="n">
-        <v>0.579</v>
+        <v>-0.6952</v>
       </c>
       <c r="V6" t="n">
         <v>0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.2836</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7889</v>
+        <v>-1.9863</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2317</v>
+        <v>0.4369</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5572</v>
+        <v>-2.4232</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2782</v>
+        <v>-1.3354</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5689</v>
+        <v>-1.2953</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7093</v>
+        <v>-0.0402</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1837</v>
+        <v>0.6449</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6855</v>
+        <v>-0.2115</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5018</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0945</v>
+        <v>-1.9804</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8834</v>
+        <v>-1.0838</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2112</v>
+        <v>-0.8966</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0228</v>
+        <v>-0.6662</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0395</v>
+        <v>-0.208</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0167</v>
+        <v>-0.4582</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9304</v>
+        <v>-1.6083</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1715</v>
+        <v>-2.1085</v>
       </c>
       <c r="E9" t="n">
-        <v>0.319</v>
+        <v>-0.3497</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4904</v>
+        <v>-1.7588</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3354</v>
+        <v>-2.2782</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2953</v>
+        <v>-1.5689</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0402</v>
+        <v>-0.7093</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6449</v>
+        <v>-0.1837</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2115</v>
+        <v>-0.6855</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.5018</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9804</v>
+        <v>-2.0945</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0838</v>
+        <v>-0.8834</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8966</v>
+        <v>-1.2112</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8514</v>
+        <v>-0.2967</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.326</v>
+        <v>-0.0784</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5254</v>
+        <v>-0.2183</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6083</v>
+        <v>0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0139</v>
+        <v>-2.407</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4387</v>
+        <v>-2.4286</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4248</v>
+        <v>0.0217</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6106</v>
+        <v>-3.1456</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.383</v>
+        <v>-1.8942</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2276</v>
+        <v>-1.2514</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6987</v>
+        <v>-1.4793</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2372</v>
+        <v>-0.1275</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4615</v>
+        <v>-1.3519</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3094</v>
+        <v>-1.6663</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6203</v>
+        <v>-1.7667</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6891</v>
+        <v>0.1005</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9432</v>
+        <v>-1.6237</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4793</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4755</v>
+        <v>-0.0294</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4778</v>
+        <v>-0.0035</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9976</v>
+        <v>-0.0259</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2836</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2525</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1235</v>
+        <v>-2.5326</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8274</v>
+        <v>-4.3373</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7039</v>
+        <v>1.8047</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8689</v>
@@ -1312,13 +1312,13 @@
         <v>3.4793</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4017</v>
+        <v>-0.8107</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5446</v>
+        <v>-0.0545</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8571</v>
+        <v>-0.7562</v>
       </c>
       <c r="V11" t="n">
         <v>3.6109</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.207799999999999</v>
+        <v>-6.834299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.262900000000001</v>
+        <v>-2.889699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9447</v>
+        <v>-3.9446</v>
       </c>
       <c r="G12" t="n">
         <v>-12.3697</v>
@@ -1369,7 +1369,7 @@
         <v>1.1858</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5840000000000001</v>
+        <v>0.5840000000000005</v>
       </c>
       <c r="M12" t="n">
         <v>-14.1398</v>
@@ -1381,7 +1381,7 @@
         <v>-3.9806</v>
       </c>
       <c r="P12" t="n">
-        <v>8.118499999999997</v>
+        <v>8.118499999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.7575</v>
@@ -1390,22 +1390,22 @@
         <v>20.8758</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.028499999999999</v>
+        <v>-3.6549</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2985999999999998</v>
+        <v>0.6722</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.327100000000001</v>
+        <v>-4.3271</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4258</v>
+        <v>7.425800000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.353599999999999</v>
+        <v>-6.3536</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.9029</v>
+        <v>7.8654</v>
       </c>
       <c r="E13" t="n">
-        <v>11.8295</v>
+        <v>8.880699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9266</v>
+        <v>-1.0154</v>
       </c>
       <c r="G13" t="n">
         <v>4.424</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>5.015</v>
+        <v>1.9775</v>
       </c>
       <c r="T13" t="n">
-        <v>4.7576</v>
+        <v>1.8088</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2574</v>
+        <v>0.1687</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6992</v>
+        <v>3.9731</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1492</v>
+        <v>2.739</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5499000000000001</v>
+        <v>1.2342</v>
       </c>
       <c r="G14" t="n">
         <v>2.1672</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8623</v>
+        <v>0.4116</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1019</v>
+        <v>0.4878</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7604</v>
+        <v>-0.0762</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6777</v>
+        <v>1.2395</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3441</v>
+        <v>0.8723</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3336</v>
+        <v>0.3672</v>
       </c>
       <c r="G15" t="n">
         <v>0.2632</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5768</v>
+        <v>0.1386</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3383</v>
+        <v>-0.1336</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2385</v>
+        <v>0.2721</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7196</v>
+        <v>0.9502</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1651</v>
+        <v>-1.2171</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4455</v>
+        <v>2.1673</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5959</v>
+        <v>1.3487</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7264</v>
+        <v>1.4357</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1305</v>
+        <v>-0.0871</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3709</v>
+        <v>0.5625</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6554</v>
+        <v>0.8003</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2845</v>
+        <v>-0.2378</v>
       </c>
       <c r="M16" t="n">
-        <v>0.225</v>
+        <v>0.7862</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.6354</v>
       </c>
       <c r="O16" t="n">
-        <v>0.154</v>
+        <v>0.1507</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1057</v>
+        <v>0.2484</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7943</v>
+        <v>-0.0272</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3115</v>
+        <v>0.2757</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.214</v>
+        <v>-0.6468</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5671</v>
       </c>
       <c r="X16" t="n">
         <v>-1.214</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0727</v>
+        <v>0.8433</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1607</v>
+        <v>1.1651</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0881</v>
+        <v>-0.3219</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3487</v>
+        <v>0.5959</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4357</v>
+        <v>0.7264</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0871</v>
+        <v>-0.1305</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5625</v>
+        <v>0.3709</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8003</v>
+        <v>0.6554</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2378</v>
+        <v>-0.2845</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7862</v>
+        <v>0.225</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6354</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1507</v>
+        <v>0.154</v>
       </c>
       <c r="P17" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7745</v>
+        <v>1.2294</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9709</v>
+        <v>0.7943</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1964</v>
+        <v>0.4351</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6468</v>
+        <v>-1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5671</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-1.214</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3591</v>
+        <v>0.3778</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8048</v>
+        <v>-0.9791</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4457</v>
+        <v>1.3569</v>
       </c>
       <c r="G18" t="n">
         <v>1.8472</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1828</v>
+        <v>0.9197</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5895</v>
+        <v>0.2361</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7723</v>
+        <v>0.6836</v>
       </c>
       <c r="V18" t="n">
         <v>0.3943</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2192</v>
+        <v>-0.2034</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0911</v>
+        <v>-0.5013</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1282</v>
+        <v>0.2979</v>
       </c>
       <c r="G19" t="n">
         <v>1.2277</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1274</v>
+        <v>0.8885</v>
       </c>
       <c r="T19" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.5977</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1353</v>
+        <v>0.2908</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0473</v>
+        <v>-1.108</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5451</v>
+        <v>-1.9533</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5023</v>
+        <v>0.8452</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7248</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.6952</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9704</v>
+        <v>0.5622</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2166</v>
+        <v>0.2031</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.8226</v>
+        <v>-0.2619</v>
       </c>
       <c r="L20" t="n">
-        <v>1.606</v>
+        <v>0.465</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5082</v>
+        <v>-0.211</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8726</v>
+        <v>-0.3082</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9764</v>
+        <v>-0.3991</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9189</v>
+        <v>-0.208</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0576</v>
+        <v>-0.1911</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7886</v>
+        <v>-1.8608</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.273</v>
+        <v>-1.453</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9266</v>
+        <v>-3.4548</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6536</v>
+        <v>2.0018</v>
       </c>
       <c r="G21" t="n">
         <v>3.2287</v>
@@ -2092,13 +2092,13 @@
         <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9528</v>
+        <v>-0.1329</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5579</v>
+        <v>-0.0861</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3949</v>
+        <v>-0.0468</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1418</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8202</v>
+        <v>-2.918</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0148</v>
+        <v>-1.6066</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1946</v>
+        <v>-1.3114</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-2.7248</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-3.6952</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5622</v>
+        <v>0.9704</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2031</v>
+        <v>-1.2166</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2619</v>
+        <v>-2.8226</v>
       </c>
       <c r="L22" t="n">
-        <v>0.465</v>
+        <v>1.606</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.211</v>
+        <v>-1.5082</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3082</v>
+        <v>-0.8726</v>
       </c>
       <c r="O22" t="n">
-        <v>0.09719999999999999</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1598</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1113</v>
+        <v>1.1057</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2696</v>
+        <v>0.8573</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8417</v>
+        <v>0.2484</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8608</v>
+        <v>0.7886</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.2079</v>
+        <v>9.5669</v>
       </c>
       <c r="E23" t="n">
-        <v>3.9448</v>
+        <v>3.944899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2629</v>
+        <v>5.621799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>12.3699</v>
@@ -2218,7 +2218,7 @@
         <v>8.973100000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>3.396599999999999</v>
+        <v>3.3966</v>
       </c>
       <c r="J23" t="n">
         <v>14.1397</v>
@@ -2227,7 +2227,7 @@
         <v>10.1591</v>
       </c>
       <c r="L23" t="n">
-        <v>3.9807</v>
+        <v>3.980700000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-1.77</v>
@@ -2236,7 +2236,7 @@
         <v>-1.1859</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.5842000000000002</v>
       </c>
       <c r="P23" t="n">
         <v>-8.1182</v>
@@ -2248,13 +2248,13 @@
         <v>12.7575</v>
       </c>
       <c r="S23" t="n">
-        <v>4.0284</v>
+        <v>6.3874</v>
       </c>
       <c r="T23" t="n">
-        <v>4.327199999999999</v>
+        <v>4.3271</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2985999999999999</v>
+        <v>2.0603</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
